--- a/GHG_Calculation/output/country_level_PI_overseas.xlsx
+++ b/GHG_Calculation/output/country_level_PI_overseas.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,82 +430,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Holdout</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N_plants</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Pop_total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N_true_types</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>True_EF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pred_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pred_median</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Pred_std</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pred_p2.5</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pred_p97.5</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PI_width</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PI_width_rel_%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RelDiff_%</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>In_PI</t>
         </is>
@@ -526,28 +538,28 @@
         <v>0.094058</v>
       </c>
       <c r="H2" t="n">
-        <v>0.255199</v>
+        <v>0.239142</v>
       </c>
       <c r="I2" t="n">
-        <v>0.20589</v>
+        <v>0.192789</v>
       </c>
       <c r="J2" t="n">
-        <v>0.172318</v>
+        <v>0.160209</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07814500000000001</v>
+        <v>0.07457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7003470000000001</v>
+        <v>0.650078</v>
       </c>
       <c r="M2" t="n">
-        <v>0.622202</v>
+        <v>0.575507</v>
       </c>
       <c r="N2" t="n">
-        <v>243.8</v>
+        <v>240.7</v>
       </c>
       <c r="O2" t="n">
-        <v>171.32</v>
+        <v>154.25</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -580,28 +592,28 @@
         <v>0.142161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035</v>
+        <v>0.104754</v>
       </c>
       <c r="I3" t="n">
-        <v>0.10178</v>
+        <v>0.103219</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01937</v>
+        <v>0.018725</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07299799999999999</v>
+        <v>0.074281</v>
       </c>
       <c r="L3" t="n">
-        <v>0.149393</v>
+        <v>0.146369</v>
       </c>
       <c r="M3" t="n">
-        <v>0.076394</v>
+        <v>0.072088</v>
       </c>
       <c r="N3" t="n">
-        <v>73.8</v>
+        <v>68.8</v>
       </c>
       <c r="O3" t="n">
-        <v>-27.2</v>
+        <v>-26.31</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -634,28 +646,28 @@
         <v>0.076807</v>
       </c>
       <c r="H4" t="n">
-        <v>0.158222</v>
+        <v>0.141708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09254</v>
+        <v>0.090561</v>
       </c>
       <c r="J4" t="n">
-        <v>0.210424</v>
+        <v>0.187342</v>
       </c>
       <c r="K4" t="n">
-        <v>0.034644</v>
+        <v>0.034774</v>
       </c>
       <c r="L4" t="n">
-        <v>0.82735</v>
+        <v>0.7087</v>
       </c>
       <c r="M4" t="n">
-        <v>0.792705</v>
+        <v>0.673926</v>
       </c>
       <c r="N4" t="n">
-        <v>501</v>
+        <v>475.6</v>
       </c>
       <c r="O4" t="n">
-        <v>106</v>
+        <v>84.5</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -688,28 +700,28 @@
         <v>0.104292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.091006</v>
+        <v>0.092512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.089754</v>
+        <v>0.093212</v>
       </c>
       <c r="J5" t="n">
-        <v>0.032665</v>
+        <v>0.025107</v>
       </c>
       <c r="K5" t="n">
-        <v>0.042375</v>
+        <v>0.046702</v>
       </c>
       <c r="L5" t="n">
-        <v>0.146436</v>
+        <v>0.132916</v>
       </c>
       <c r="M5" t="n">
-        <v>0.104061</v>
+        <v>0.086214</v>
       </c>
       <c r="N5" t="n">
-        <v>114.3</v>
+        <v>93.2</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.74</v>
+        <v>-11.3</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -739,31 +751,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.398874</v>
+        <v>0.406462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.446131</v>
+        <v>0.436895</v>
       </c>
       <c r="I6" t="n">
-        <v>0.405842</v>
+        <v>0.397234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.186508</v>
+        <v>0.178307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.200146</v>
+        <v>0.200641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.902494</v>
+        <v>0.867795</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7023470000000001</v>
+        <v>0.667154</v>
       </c>
       <c r="N6" t="n">
-        <v>157.4</v>
+        <v>152.7</v>
       </c>
       <c r="O6" t="n">
-        <v>11.85</v>
+        <v>7.49</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -793,31 +805,31 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.045196</v>
+        <v>0.045008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.042657</v>
+        <v>0.043132</v>
       </c>
       <c r="I7" t="n">
-        <v>0.041346</v>
+        <v>0.041533</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009067</v>
+        <v>0.010288</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03051</v>
+        <v>0.031021</v>
       </c>
       <c r="L7" t="n">
-        <v>0.061303</v>
+        <v>0.06365800000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.030793</v>
+        <v>0.032637</v>
       </c>
       <c r="N7" t="n">
-        <v>72.2</v>
+        <v>75.7</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.62</v>
+        <v>-4.17</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -847,31 +859,31 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.661902</v>
+        <v>0.663887</v>
       </c>
       <c r="H8" t="n">
-        <v>0.675381</v>
+        <v>0.678077</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671171</v>
+        <v>0.67495</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07087</v>
+        <v>0.071587</v>
       </c>
       <c r="K8" t="n">
-        <v>0.549421</v>
+        <v>0.5507649999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.82741</v>
+        <v>0.830775</v>
       </c>
       <c r="M8" t="n">
-        <v>0.277989</v>
+        <v>0.28001</v>
       </c>
       <c r="N8" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -904,28 +916,28 @@
         <v>0.020938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.022473</v>
+        <v>0.022416</v>
       </c>
       <c r="I9" t="n">
-        <v>0.022252</v>
+        <v>0.022195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002373</v>
+        <v>0.002259</v>
       </c>
       <c r="K9" t="n">
-        <v>0.018865</v>
+        <v>0.018927</v>
       </c>
       <c r="L9" t="n">
-        <v>0.027363</v>
+        <v>0.02705</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008498</v>
+        <v>0.008123</v>
       </c>
       <c r="N9" t="n">
-        <v>37.8</v>
+        <v>36.2</v>
       </c>
       <c r="O9" t="n">
-        <v>7.33</v>
+        <v>7.06</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -958,28 +970,28 @@
         <v>0.569754</v>
       </c>
       <c r="H10" t="n">
-        <v>0.628418</v>
+        <v>0.628054</v>
       </c>
       <c r="I10" t="n">
-        <v>0.621208</v>
+        <v>0.618832</v>
       </c>
       <c r="J10" t="n">
-        <v>0.082258</v>
+        <v>0.08319799999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.492133</v>
+        <v>0.490203</v>
       </c>
       <c r="L10" t="n">
-        <v>0.810445</v>
+        <v>0.810485</v>
       </c>
       <c r="M10" t="n">
-        <v>0.318312</v>
+        <v>0.320283</v>
       </c>
       <c r="N10" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>10.3</v>
+        <v>10.23</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1012,28 +1024,28 @@
         <v>0.030584</v>
       </c>
       <c r="H11" t="n">
-        <v>0.031185</v>
+        <v>0.031072</v>
       </c>
       <c r="I11" t="n">
-        <v>0.030757</v>
+        <v>0.030686</v>
       </c>
       <c r="J11" t="n">
-        <v>0.003529</v>
+        <v>0.003419</v>
       </c>
       <c r="K11" t="n">
-        <v>0.026428</v>
+        <v>0.026331</v>
       </c>
       <c r="L11" t="n">
-        <v>0.038198</v>
+        <v>0.038002</v>
       </c>
       <c r="M11" t="n">
-        <v>0.011771</v>
+        <v>0.011671</v>
       </c>
       <c r="N11" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1066,28 +1078,28 @@
         <v>0.396725</v>
       </c>
       <c r="H12" t="n">
-        <v>0.465155</v>
+        <v>0.455411</v>
       </c>
       <c r="I12" t="n">
-        <v>0.212364</v>
+        <v>0.218522</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5976669999999999</v>
+        <v>0.568218</v>
       </c>
       <c r="K12" t="n">
-        <v>0.051258</v>
+        <v>0.052051</v>
       </c>
       <c r="L12" t="n">
-        <v>1.861264</v>
+        <v>1.812265</v>
       </c>
       <c r="M12" t="n">
-        <v>1.810006</v>
+        <v>1.760215</v>
       </c>
       <c r="N12" t="n">
-        <v>389.1</v>
+        <v>386.5</v>
       </c>
       <c r="O12" t="n">
-        <v>17.25</v>
+        <v>14.79</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1120,28 +1132,28 @@
         <v>0.034655</v>
       </c>
       <c r="H13" t="n">
-        <v>0.034485</v>
+        <v>0.034394</v>
       </c>
       <c r="I13" t="n">
-        <v>0.026443</v>
+        <v>0.026589</v>
       </c>
       <c r="J13" t="n">
-        <v>0.028934</v>
+        <v>0.030418</v>
       </c>
       <c r="K13" t="n">
-        <v>0.009095000000000001</v>
+        <v>0.009109000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.105012</v>
+        <v>0.102637</v>
       </c>
       <c r="M13" t="n">
-        <v>0.095916</v>
+        <v>0.093529</v>
       </c>
       <c r="N13" t="n">
-        <v>278.1</v>
+        <v>271.9</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.49</v>
+        <v>-0.75</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1174,28 +1186,28 @@
         <v>0.525877</v>
       </c>
       <c r="H14" t="n">
-        <v>0.553462</v>
+        <v>0.548111</v>
       </c>
       <c r="I14" t="n">
-        <v>0.520445</v>
+        <v>0.512995</v>
       </c>
       <c r="J14" t="n">
-        <v>0.259252</v>
+        <v>0.263478</v>
       </c>
       <c r="K14" t="n">
-        <v>0.173857</v>
+        <v>0.173687</v>
       </c>
       <c r="L14" t="n">
-        <v>1.153087</v>
+        <v>1.151515</v>
       </c>
       <c r="M14" t="n">
-        <v>0.979231</v>
+        <v>0.977828</v>
       </c>
       <c r="N14" t="n">
-        <v>176.9</v>
+        <v>178.4</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>4.23</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1228,28 +1240,28 @@
         <v>0.023215</v>
       </c>
       <c r="H15" t="n">
-        <v>0.027603</v>
+        <v>0.027579</v>
       </c>
       <c r="I15" t="n">
-        <v>0.025341</v>
+        <v>0.02514</v>
       </c>
       <c r="J15" t="n">
-        <v>0.012505</v>
+        <v>0.012701</v>
       </c>
       <c r="K15" t="n">
-        <v>0.012838</v>
+        <v>0.012482</v>
       </c>
       <c r="L15" t="n">
-        <v>0.052612</v>
+        <v>0.054791</v>
       </c>
       <c r="M15" t="n">
-        <v>0.039774</v>
+        <v>0.042309</v>
       </c>
       <c r="N15" t="n">
-        <v>144.1</v>
+        <v>153.4</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1282,28 +1294,28 @@
         <v>0.8794380000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8181929999999999</v>
+        <v>0.819744</v>
       </c>
       <c r="I16" t="n">
-        <v>0.80419</v>
+        <v>0.805352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.139212</v>
+        <v>0.140063</v>
       </c>
       <c r="K16" t="n">
-        <v>0.584287</v>
+        <v>0.581043</v>
       </c>
       <c r="L16" t="n">
-        <v>1.121895</v>
+        <v>1.135697</v>
       </c>
       <c r="M16" t="n">
-        <v>0.537608</v>
+        <v>0.554654</v>
       </c>
       <c r="N16" t="n">
-        <v>65.7</v>
+        <v>67.7</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.96</v>
+        <v>-6.79</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1336,28 +1348,28 @@
         <v>0.088627</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07084</v>
+        <v>0.07301100000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06909800000000001</v>
+        <v>0.07116599999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.016419</v>
+        <v>0.016586</v>
       </c>
       <c r="K17" t="n">
-        <v>0.043159</v>
+        <v>0.045524</v>
       </c>
       <c r="L17" t="n">
-        <v>0.108281</v>
+        <v>0.11047</v>
       </c>
       <c r="M17" t="n">
-        <v>0.065122</v>
+        <v>0.064946</v>
       </c>
       <c r="N17" t="n">
-        <v>91.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="O17" t="n">
-        <v>-20.07</v>
+        <v>-17.62</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1390,28 +1402,28 @@
         <v>0.619864</v>
       </c>
       <c r="H18" t="n">
-        <v>0.435276</v>
+        <v>0.44396</v>
       </c>
       <c r="I18" t="n">
-        <v>0.303276</v>
+        <v>0.316193</v>
       </c>
       <c r="J18" t="n">
-        <v>0.383839</v>
+        <v>0.382083</v>
       </c>
       <c r="K18" t="n">
-        <v>0.089853</v>
+        <v>0.092863</v>
       </c>
       <c r="L18" t="n">
-        <v>1.418646</v>
+        <v>1.408084</v>
       </c>
       <c r="M18" t="n">
-        <v>1.328793</v>
+        <v>1.315221</v>
       </c>
       <c r="N18" t="n">
-        <v>305.3</v>
+        <v>296.2</v>
       </c>
       <c r="O18" t="n">
-        <v>-29.78</v>
+        <v>-28.38</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -1444,28 +1456,28 @@
         <v>0.019212</v>
       </c>
       <c r="H19" t="n">
-        <v>0.043443</v>
+        <v>0.041322</v>
       </c>
       <c r="I19" t="n">
-        <v>0.037737</v>
+        <v>0.036023</v>
       </c>
       <c r="J19" t="n">
-        <v>0.025385</v>
+        <v>0.024164</v>
       </c>
       <c r="K19" t="n">
-        <v>0.015146</v>
+        <v>0.014185</v>
       </c>
       <c r="L19" t="n">
-        <v>0.101782</v>
+        <v>0.095279</v>
       </c>
       <c r="M19" t="n">
-        <v>0.086636</v>
+        <v>0.081094</v>
       </c>
       <c r="N19" t="n">
-        <v>199.4</v>
+        <v>196.2</v>
       </c>
       <c r="O19" t="n">
-        <v>126.12</v>
+        <v>115.08</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1498,28 +1510,28 @@
         <v>0.447074</v>
       </c>
       <c r="H20" t="n">
-        <v>0.445157</v>
+        <v>0.444627</v>
       </c>
       <c r="I20" t="n">
-        <v>0.437626</v>
+        <v>0.437795</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09058099999999999</v>
+        <v>0.08960899999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.289345</v>
+        <v>0.292035</v>
       </c>
       <c r="L20" t="n">
-        <v>0.636781</v>
+        <v>0.6364069999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.347436</v>
+        <v>0.344371</v>
       </c>
       <c r="N20" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.43</v>
+        <v>-0.55</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1552,28 +1564,28 @@
         <v>0.021667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.022877</v>
+        <v>0.022761</v>
       </c>
       <c r="I21" t="n">
-        <v>0.022365</v>
+        <v>0.022224</v>
       </c>
       <c r="J21" t="n">
-        <v>0.004029</v>
+        <v>0.00395</v>
       </c>
       <c r="K21" t="n">
-        <v>0.017234</v>
+        <v>0.017145</v>
       </c>
       <c r="L21" t="n">
-        <v>0.031841</v>
+        <v>0.031345</v>
       </c>
       <c r="M21" t="n">
-        <v>0.014608</v>
+        <v>0.014199</v>
       </c>
       <c r="N21" t="n">
-        <v>63.9</v>
+        <v>62.4</v>
       </c>
       <c r="O21" t="n">
-        <v>5.58</v>
+        <v>5.04</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1606,28 +1618,28 @@
         <v>0.453489</v>
       </c>
       <c r="H22" t="n">
-        <v>0.408797</v>
+        <v>0.429221</v>
       </c>
       <c r="I22" t="n">
-        <v>0.172895</v>
+        <v>0.18719</v>
       </c>
       <c r="J22" t="n">
-        <v>0.532151</v>
+        <v>0.533036</v>
       </c>
       <c r="K22" t="n">
-        <v>0.031744</v>
+        <v>0.030077</v>
       </c>
       <c r="L22" t="n">
-        <v>1.90279</v>
+        <v>1.895119</v>
       </c>
       <c r="M22" t="n">
-        <v>1.871046</v>
+        <v>1.865042</v>
       </c>
       <c r="N22" t="n">
-        <v>457.7</v>
+        <v>434.5</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.859999999999999</v>
+        <v>-5.35</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -1660,28 +1672,28 @@
         <v>0.022207</v>
       </c>
       <c r="H23" t="n">
-        <v>0.030952</v>
+        <v>0.031574</v>
       </c>
       <c r="I23" t="n">
-        <v>0.021559</v>
+        <v>0.02107</v>
       </c>
       <c r="J23" t="n">
-        <v>0.033941</v>
+        <v>0.043349</v>
       </c>
       <c r="K23" t="n">
-        <v>0.004065</v>
+        <v>0.00413</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112341</v>
+        <v>0.111223</v>
       </c>
       <c r="M23" t="n">
-        <v>0.108276</v>
+        <v>0.107093</v>
       </c>
       <c r="N23" t="n">
-        <v>349.8</v>
+        <v>339.2</v>
       </c>
       <c r="O23" t="n">
-        <v>39.38</v>
+        <v>42.18</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -1714,28 +1726,28 @@
         <v>0.744459</v>
       </c>
       <c r="H24" t="n">
-        <v>0.591728</v>
+        <v>0.574072</v>
       </c>
       <c r="I24" t="n">
-        <v>0.485902</v>
+        <v>0.470214</v>
       </c>
       <c r="J24" t="n">
-        <v>0.349057</v>
+        <v>0.33549</v>
       </c>
       <c r="K24" t="n">
-        <v>0.173423</v>
+        <v>0.17451</v>
       </c>
       <c r="L24" t="n">
-        <v>1.367925</v>
+        <v>1.331798</v>
       </c>
       <c r="M24" t="n">
-        <v>1.194502</v>
+        <v>1.157288</v>
       </c>
       <c r="N24" t="n">
-        <v>201.9</v>
+        <v>201.6</v>
       </c>
       <c r="O24" t="n">
-        <v>-20.52</v>
+        <v>-22.89</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -1768,28 +1780,28 @@
         <v>0.024001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.027929</v>
+        <v>0.028082</v>
       </c>
       <c r="I25" t="n">
-        <v>0.024817</v>
+        <v>0.025405</v>
       </c>
       <c r="J25" t="n">
-        <v>0.015893</v>
+        <v>0.015792</v>
       </c>
       <c r="K25" t="n">
-        <v>0.011244</v>
+        <v>0.011189</v>
       </c>
       <c r="L25" t="n">
-        <v>0.062083</v>
+        <v>0.060196</v>
       </c>
       <c r="M25" t="n">
-        <v>0.050839</v>
+        <v>0.049006</v>
       </c>
       <c r="N25" t="n">
-        <v>182</v>
+        <v>174.5</v>
       </c>
       <c r="O25" t="n">
-        <v>16.36</v>
+        <v>17</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -1822,28 +1834,28 @@
         <v>0.44888</v>
       </c>
       <c r="H26" t="n">
-        <v>0.45659</v>
+        <v>0.45739</v>
       </c>
       <c r="I26" t="n">
-        <v>0.323912</v>
+        <v>0.329861</v>
       </c>
       <c r="J26" t="n">
-        <v>0.346469</v>
+        <v>0.345565</v>
       </c>
       <c r="K26" t="n">
-        <v>0.121438</v>
+        <v>0.127841</v>
       </c>
       <c r="L26" t="n">
-        <v>1.339913</v>
+        <v>1.333994</v>
       </c>
       <c r="M26" t="n">
-        <v>1.218475</v>
+        <v>1.206153</v>
       </c>
       <c r="N26" t="n">
-        <v>266.9</v>
+        <v>263.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -1876,28 +1888,28 @@
         <v>0.039739</v>
       </c>
       <c r="H27" t="n">
-        <v>0.060155</v>
+        <v>0.058748</v>
       </c>
       <c r="I27" t="n">
-        <v>0.053169</v>
+        <v>0.051834</v>
       </c>
       <c r="J27" t="n">
-        <v>0.034909</v>
+        <v>0.036392</v>
       </c>
       <c r="K27" t="n">
-        <v>0.017479</v>
+        <v>0.017099</v>
       </c>
       <c r="L27" t="n">
-        <v>0.136975</v>
+        <v>0.136395</v>
       </c>
       <c r="M27" t="n">
-        <v>0.119496</v>
+        <v>0.119296</v>
       </c>
       <c r="N27" t="n">
-        <v>198.6</v>
+        <v>203.1</v>
       </c>
       <c r="O27" t="n">
-        <v>51.38</v>
+        <v>47.83</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -1927,31 +1939,31 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.406838</v>
+        <v>0.407029</v>
       </c>
       <c r="H28" t="n">
-        <v>0.372971</v>
+        <v>0.372885</v>
       </c>
       <c r="I28" t="n">
-        <v>0.326945</v>
+        <v>0.324973</v>
       </c>
       <c r="J28" t="n">
-        <v>0.161234</v>
+        <v>0.168153</v>
       </c>
       <c r="K28" t="n">
-        <v>0.177981</v>
+        <v>0.175037</v>
       </c>
       <c r="L28" t="n">
-        <v>0.773636</v>
+        <v>0.787727</v>
       </c>
       <c r="M28" t="n">
-        <v>0.595655</v>
+        <v>0.61269</v>
       </c>
       <c r="N28" t="n">
-        <v>159.7</v>
+        <v>164.3</v>
       </c>
       <c r="O28" t="n">
-        <v>-8.32</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -1981,31 +1993,31 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.03935</v>
+        <v>0.039345</v>
       </c>
       <c r="H29" t="n">
-        <v>0.045517</v>
+        <v>0.045243</v>
       </c>
       <c r="I29" t="n">
-        <v>0.044097</v>
+        <v>0.043785</v>
       </c>
       <c r="J29" t="n">
-        <v>0.009847</v>
+        <v>0.010397</v>
       </c>
       <c r="K29" t="n">
-        <v>0.031948</v>
+        <v>0.031262</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06673999999999999</v>
+        <v>0.06757299999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.034791</v>
+        <v>0.036311</v>
       </c>
       <c r="N29" t="n">
-        <v>76.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="O29" t="n">
-        <v>15.67</v>
+        <v>14.99</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2038,28 +2050,28 @@
         <v>0.251681</v>
       </c>
       <c r="H30" t="n">
-        <v>0.513392</v>
+        <v>0.507841</v>
       </c>
       <c r="I30" t="n">
-        <v>0.445972</v>
+        <v>0.440443</v>
       </c>
       <c r="J30" t="n">
-        <v>0.28181</v>
+        <v>0.274536</v>
       </c>
       <c r="K30" t="n">
-        <v>0.18551</v>
+        <v>0.188912</v>
       </c>
       <c r="L30" t="n">
-        <v>1.235709</v>
+        <v>1.238401</v>
       </c>
       <c r="M30" t="n">
-        <v>1.050199</v>
+        <v>1.049488</v>
       </c>
       <c r="N30" t="n">
-        <v>204.6</v>
+        <v>206.7</v>
       </c>
       <c r="O30" t="n">
-        <v>103.99</v>
+        <v>101.78</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2092,28 +2104,28 @@
         <v>0.06254999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.048856</v>
+        <v>0.049001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.044467</v>
+        <v>0.044833</v>
       </c>
       <c r="J31" t="n">
-        <v>0.019937</v>
+        <v>0.019126</v>
       </c>
       <c r="K31" t="n">
-        <v>0.024046</v>
+        <v>0.024227</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08469400000000001</v>
+        <v>0.084732</v>
       </c>
       <c r="M31" t="n">
-        <v>0.060648</v>
+        <v>0.060505</v>
       </c>
       <c r="N31" t="n">
-        <v>124.1</v>
+        <v>123.5</v>
       </c>
       <c r="O31" t="n">
-        <v>-21.89</v>
+        <v>-21.66</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2146,28 +2158,28 @@
         <v>0.443433</v>
       </c>
       <c r="H32" t="n">
-        <v>0.522765</v>
+        <v>0.496077</v>
       </c>
       <c r="I32" t="n">
-        <v>0.453073</v>
+        <v>0.429323</v>
       </c>
       <c r="J32" t="n">
-        <v>0.340004</v>
+        <v>0.328784</v>
       </c>
       <c r="K32" t="n">
-        <v>0.098522</v>
+        <v>0.095314</v>
       </c>
       <c r="L32" t="n">
-        <v>1.367174</v>
+        <v>1.327442</v>
       </c>
       <c r="M32" t="n">
-        <v>1.268652</v>
+        <v>1.232128</v>
       </c>
       <c r="N32" t="n">
-        <v>242.7</v>
+        <v>248.4</v>
       </c>
       <c r="O32" t="n">
-        <v>17.89</v>
+        <v>11.87</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2200,28 +2212,28 @@
         <v>0.02211</v>
       </c>
       <c r="H33" t="n">
-        <v>0.024261</v>
+        <v>0.023847</v>
       </c>
       <c r="I33" t="n">
-        <v>0.022255</v>
+        <v>0.021838</v>
       </c>
       <c r="J33" t="n">
-        <v>0.011683</v>
+        <v>0.011982</v>
       </c>
       <c r="K33" t="n">
-        <v>0.008982</v>
+        <v>0.008808</v>
       </c>
       <c r="L33" t="n">
-        <v>0.051279</v>
+        <v>0.051963</v>
       </c>
       <c r="M33" t="n">
-        <v>0.042297</v>
+        <v>0.043155</v>
       </c>
       <c r="N33" t="n">
-        <v>174.3</v>
+        <v>181</v>
       </c>
       <c r="O33" t="n">
-        <v>9.73</v>
+        <v>7.85</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2251,31 +2263,31 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.855817</v>
+        <v>0.867051</v>
       </c>
       <c r="H34" t="n">
-        <v>0.668913</v>
+        <v>0.677986</v>
       </c>
       <c r="I34" t="n">
-        <v>0.645228</v>
+        <v>0.651681</v>
       </c>
       <c r="J34" t="n">
-        <v>0.194777</v>
+        <v>0.193083</v>
       </c>
       <c r="K34" t="n">
-        <v>0.364664</v>
+        <v>0.374519</v>
       </c>
       <c r="L34" t="n">
-        <v>1.118701</v>
+        <v>1.124711</v>
       </c>
       <c r="M34" t="n">
-        <v>0.754037</v>
+        <v>0.750192</v>
       </c>
       <c r="N34" t="n">
-        <v>112.7</v>
+        <v>110.7</v>
       </c>
       <c r="O34" t="n">
-        <v>-21.84</v>
+        <v>-21.81</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2305,31 +2317,31 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.020369</v>
+        <v>0.020112</v>
       </c>
       <c r="H35" t="n">
-        <v>0.023005</v>
+        <v>0.022866</v>
       </c>
       <c r="I35" t="n">
-        <v>0.022146</v>
+        <v>0.02194</v>
       </c>
       <c r="J35" t="n">
-        <v>0.006007</v>
+        <v>0.006004</v>
       </c>
       <c r="K35" t="n">
-        <v>0.014749</v>
+        <v>0.014921</v>
       </c>
       <c r="L35" t="n">
-        <v>0.035234</v>
+        <v>0.035568</v>
       </c>
       <c r="M35" t="n">
-        <v>0.020485</v>
+        <v>0.020646</v>
       </c>
       <c r="N35" t="n">
-        <v>89</v>
+        <v>90.3</v>
       </c>
       <c r="O35" t="n">
-        <v>12.94</v>
+        <v>13.7</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2362,28 +2374,28 @@
         <v>0.300675</v>
       </c>
       <c r="H36" t="n">
-        <v>0.387616</v>
+        <v>0.386959</v>
       </c>
       <c r="I36" t="n">
-        <v>0.344492</v>
+        <v>0.341852</v>
       </c>
       <c r="J36" t="n">
-        <v>0.195239</v>
+        <v>0.194049</v>
       </c>
       <c r="K36" t="n">
-        <v>0.134913</v>
+        <v>0.138003</v>
       </c>
       <c r="L36" t="n">
-        <v>0.856769</v>
+        <v>0.844614</v>
       </c>
       <c r="M36" t="n">
-        <v>0.721855</v>
+        <v>0.706611</v>
       </c>
       <c r="N36" t="n">
-        <v>186.2</v>
+        <v>182.6</v>
       </c>
       <c r="O36" t="n">
-        <v>28.92</v>
+        <v>28.7</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -2416,28 +2428,28 @@
         <v>0.049343</v>
       </c>
       <c r="H37" t="n">
-        <v>0.040167</v>
+        <v>0.038649</v>
       </c>
       <c r="I37" t="n">
-        <v>0.038239</v>
+        <v>0.036883</v>
       </c>
       <c r="J37" t="n">
-        <v>0.011896</v>
+        <v>0.011036</v>
       </c>
       <c r="K37" t="n">
-        <v>0.024414</v>
+        <v>0.024012</v>
       </c>
       <c r="L37" t="n">
-        <v>0.06561599999999999</v>
+        <v>0.062427</v>
       </c>
       <c r="M37" t="n">
-        <v>0.041201</v>
+        <v>0.038415</v>
       </c>
       <c r="N37" t="n">
-        <v>102.6</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>-18.6</v>
+        <v>-21.67</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -2470,28 +2482,28 @@
         <v>0.504517</v>
       </c>
       <c r="H38" t="n">
-        <v>0.408016</v>
+        <v>0.400664</v>
       </c>
       <c r="I38" t="n">
-        <v>0.362449</v>
+        <v>0.355184</v>
       </c>
       <c r="J38" t="n">
-        <v>0.220125</v>
+        <v>0.212149</v>
       </c>
       <c r="K38" t="n">
-        <v>0.119814</v>
+        <v>0.119476</v>
       </c>
       <c r="L38" t="n">
-        <v>0.952504</v>
+        <v>0.904628</v>
       </c>
       <c r="M38" t="n">
-        <v>0.83269</v>
+        <v>0.785152</v>
       </c>
       <c r="N38" t="n">
-        <v>204.1</v>
+        <v>196</v>
       </c>
       <c r="O38" t="n">
-        <v>-19.13</v>
+        <v>-20.58</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -2524,28 +2536,28 @@
         <v>0.02195</v>
       </c>
       <c r="H39" t="n">
-        <v>0.034051</v>
+        <v>0.034033</v>
       </c>
       <c r="I39" t="n">
-        <v>0.032301</v>
+        <v>0.031698</v>
       </c>
       <c r="J39" t="n">
-        <v>0.012761</v>
+        <v>0.013616</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01689</v>
+        <v>0.01663</v>
       </c>
       <c r="L39" t="n">
-        <v>0.060073</v>
+        <v>0.06216</v>
       </c>
       <c r="M39" t="n">
-        <v>0.043183</v>
+        <v>0.045531</v>
       </c>
       <c r="N39" t="n">
-        <v>126.8</v>
+        <v>133.8</v>
       </c>
       <c r="O39" t="n">
-        <v>55.13</v>
+        <v>55.05</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -2575,31 +2587,31 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.450725</v>
+        <v>0.451032</v>
       </c>
       <c r="H40" t="n">
-        <v>0.522071</v>
+        <v>0.519296</v>
       </c>
       <c r="I40" t="n">
-        <v>0.513424</v>
+        <v>0.511311</v>
       </c>
       <c r="J40" t="n">
-        <v>0.085827</v>
+        <v>0.08426</v>
       </c>
       <c r="K40" t="n">
-        <v>0.381303</v>
+        <v>0.383373</v>
       </c>
       <c r="L40" t="n">
-        <v>0.710933</v>
+        <v>0.701394</v>
       </c>
       <c r="M40" t="n">
-        <v>0.32963</v>
+        <v>0.318021</v>
       </c>
       <c r="N40" t="n">
-        <v>63.1</v>
+        <v>61.2</v>
       </c>
       <c r="O40" t="n">
-        <v>15.83</v>
+        <v>15.14</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -2629,31 +2641,31 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.025879</v>
+        <v>0.025876</v>
       </c>
       <c r="H41" t="n">
-        <v>0.023032</v>
+        <v>0.022888</v>
       </c>
       <c r="I41" t="n">
-        <v>0.022769</v>
+        <v>0.022552</v>
       </c>
       <c r="J41" t="n">
-        <v>0.002655</v>
+        <v>0.002897</v>
       </c>
       <c r="K41" t="n">
-        <v>0.018714</v>
+        <v>0.018658</v>
       </c>
       <c r="L41" t="n">
-        <v>0.028837</v>
+        <v>0.02898</v>
       </c>
       <c r="M41" t="n">
-        <v>0.010124</v>
+        <v>0.010322</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>45.1</v>
       </c>
       <c r="O41" t="n">
-        <v>-11</v>
+        <v>-11.55</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -2674,57 +2686,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Holdout</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>N_countries</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RelDiff_mean_%</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RelDiff_std_%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RelDiff_min_%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RelDiff_max_%</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MedAbs_RelDiff_%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PI_width_rel_mean_%</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PI_coverage_%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>N_covered</t>
         </is>
@@ -2743,22 +2755,22 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.85</v>
+        <v>1.13</v>
       </c>
       <c r="E2" t="n">
-        <v>12.26</v>
+        <v>11.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.07</v>
+        <v>-17.62</v>
       </c>
       <c r="G2" t="n">
-        <v>15.67</v>
+        <v>14.99</v>
       </c>
       <c r="H2" t="n">
-        <v>9.16</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>64.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
@@ -2782,22 +2794,22 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="E3" t="n">
-        <v>12.51</v>
+        <v>11.87</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.84</v>
+        <v>-21.81</v>
       </c>
       <c r="G3" t="n">
-        <v>15.83</v>
+        <v>15.14</v>
       </c>
       <c r="H3" t="n">
-        <v>9.31</v>
+        <v>7.94</v>
       </c>
       <c r="I3" t="n">
-        <v>91.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
@@ -2821,22 +2833,22 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>19.67</v>
+        <v>18.51</v>
       </c>
       <c r="E4" t="n">
-        <v>43.63</v>
+        <v>41.22</v>
       </c>
       <c r="F4" t="n">
-        <v>-27.2</v>
+        <v>-26.31</v>
       </c>
       <c r="G4" t="n">
-        <v>126.12</v>
+        <v>115.08</v>
       </c>
       <c r="H4" t="n">
-        <v>20.4</v>
+        <v>21.66</v>
       </c>
       <c r="I4" t="n">
-        <v>172.3</v>
+        <v>169.8</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
@@ -2860,22 +2872,22 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09</v>
+        <v>27.07</v>
       </c>
       <c r="E5" t="n">
-        <v>62.57</v>
+        <v>56.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-29.78</v>
+        <v>-28.38</v>
       </c>
       <c r="G5" t="n">
-        <v>171.32</v>
+        <v>154.25</v>
       </c>
       <c r="H5" t="n">
-        <v>19.82</v>
+        <v>21.74</v>
       </c>
       <c r="I5" t="n">
-        <v>281.7</v>
+        <v>275.9</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
